--- a/results/mi355x_gptoss120b_mxfp4/mi355x_gptoss120b_mxfp4_mtp0_ep1_tp1_atom_dev_profiling/decode_breakdown_c64.xlsx
+++ b/results/mi355x_gptoss120b_mxfp4/mi355x_gptoss120b_mxfp4_mtp0_ep1_tp1_atom_dev_profiling/decode_breakdown_c64.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="decode" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kernel_summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="attn_decode" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="attn_summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="non_attn_decode" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="non_attn_summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,37 +479,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>rope_and_kv_cache</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>_fused_add_rmsnorm_pad</t>
+          <t>_fused_qk_rope_reshape_and_cache_kernel</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.679</v>
+        <v>5.519</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1</v>
+        <v>40.5</v>
       </c>
       <c r="E2" t="n">
-        <v>5.679</v>
+        <v>5.519</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1</v>
+        <v>40.5</v>
       </c>
       <c r="G2" t="n">
-        <v>5.801</v>
+        <v>5.572</v>
       </c>
       <c r="H2" t="n">
-        <v>5.679</v>
+        <v>5.439</v>
       </c>
       <c r="I2" t="n">
-        <v>7.08</v>
+        <v>6.799</v>
       </c>
       <c r="J2" t="n">
-        <v>5.801</v>
+        <v>5.572</v>
       </c>
       <c r="K2" t="n">
         <v>520</v>
@@ -516,37 +518,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>triton_poi</t>
+          <t>attention</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>triton_poi_fused_as_strided_clone_1</t>
+          <t>paged_attention_decode_sliding_window</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.08</v>
+        <v>8.119</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6</v>
+        <v>59.5</v>
       </c>
       <c r="E3" t="n">
-        <v>7.08</v>
+        <v>8.119</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>59.5</v>
       </c>
       <c r="G3" t="n">
-        <v>5.704</v>
+        <v>12.178</v>
       </c>
       <c r="H3" t="n">
-        <v>5.679</v>
+        <v>14.919</v>
       </c>
       <c r="I3" t="n">
-        <v>6.999</v>
+        <v>16.839</v>
       </c>
       <c r="J3" t="n">
-        <v>5.704</v>
+        <v>12.178</v>
       </c>
       <c r="K3" t="n">
         <v>520</v>
@@ -555,469 +557,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gemm_a16w16</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>aiter::bf16gemm_fp32bf16_tn_64x64_splitk_clean</t>
-        </is>
-      </c>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>5.719</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>5.719</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2.1</v>
+        <v>13.638</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="G4" t="n">
-        <v>6.824</v>
-      </c>
-      <c r="H4" t="n">
-        <v>7.039</v>
-      </c>
-      <c r="I4" t="n">
-        <v>7.439</v>
-      </c>
-      <c r="J4" t="n">
-        <v>6.824</v>
-      </c>
+        <v>17.749</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>void vllm::moe::topkGatingSoftmax&lt;std::bfloat16_t, 16, 128, 8, 32, true, 0, (vllm::moe::SharedExpertScoringFunc)0&gt;(std::bfloat16_t const*, bool const*, float*, int, int*, int*, int, int, int, int, int, int)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>5.639</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5.639</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5.944</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5.679</v>
-      </c>
-      <c r="I5" t="n">
-        <v>7.119</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5.944</v>
-      </c>
-      <c r="K5" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>mxfp4_moe</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>void ck_tile::kentry&lt;2, ck_tile::MoeSortingMultiPhaseKernel_P0_v2&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;, ck_tile::MoeSortingMultiPhaseKernel_P0_v2&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;::Kargs&gt;(ck_tile::MoeSortingMultiPhaseKernel_P0_v2&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;::Kargs)</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>5.679</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>11.278</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5.792</v>
-      </c>
-      <c r="H6" t="n">
-        <v>5.679</v>
-      </c>
-      <c r="I6" t="n">
-        <v>7.079</v>
-      </c>
-      <c r="J6" t="n">
-        <v>11.547</v>
-      </c>
-      <c r="K6" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>void ck_tile::kentry&lt;2, ck_tile::MoeSortingMultiPhaseKernel_P23&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;, ck_tile::MoeSortingMultiPhaseKernel_P23&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;::Kargs&gt;(ck_tile::MoeSortingMultiPhaseKernel_P23&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;::Kargs)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5.599</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
-        <v>5.755</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5.679</v>
-      </c>
-      <c r="I7" t="n">
-        <v>7.039</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>v_up_proj_and_o_proj</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>void ck_tile::kentry&lt;2, ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)1, ck_tile::moe::Swiglu&gt;, ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)1, ck_tile::moe::Swiglu&gt;::MoeFlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt; &gt; &gt;(ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)1, ck_tile::moe::Swiglu&gt;::MoeFlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt; &gt;)</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>108.68</v>
-      </c>
-      <c r="D8" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="E8" t="n">
-        <v>170.479</v>
-      </c>
-      <c r="F8" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>102.036</v>
-      </c>
-      <c r="H8" t="n">
-        <v>101.56</v>
-      </c>
-      <c r="I8" t="n">
-        <v>112.88</v>
-      </c>
-      <c r="J8" t="n">
-        <v>158.715</v>
-      </c>
-      <c r="K8" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>void ck_tile::kentry&lt;2, ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)2, ck_tile::moe::MoeSilu&gt;, ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)2, ck_tile::moe::MoeSilu&gt;::MoeFlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt; &gt; &gt;(ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)2, ck_tile::moe::MoeSilu&gt;::MoeFlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt; &gt;)</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>61.799</v>
-      </c>
-      <c r="D9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="n">
-        <v>56.679</v>
-      </c>
-      <c r="H9" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>62.359</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hipLaunchKernel</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>void aiter::add_rmsnorm_quant_kernel&lt;std::bfloat16_t, std::bfloat16_t, 256, 16, true, false, true, 1&gt;(std::bfloat16_t*, std::bfloat16_t*, float*, std::bfloat16_t*, std::bfloat16_t*, std::bfloat16_t*, double, int, int, int, int, int, int, int, bool)</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>7.079</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E10" t="n">
-        <v>7.079</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="G10" t="n">
-        <v>5.688</v>
-      </c>
-      <c r="H10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6.959</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5.688</v>
-      </c>
-      <c r="K10" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>gemm_a16w16</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>aiter::bf16gemm_fp32bf16_tn_64x64_splitk_clean</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>14.159</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>14.159</v>
-      </c>
-      <c r="F11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13.881</v>
-      </c>
-      <c r="H11" t="n">
-        <v>14.119</v>
-      </c>
-      <c r="I11" t="n">
-        <v>14.28</v>
-      </c>
-      <c r="J11" t="n">
-        <v>13.881</v>
-      </c>
-      <c r="K11" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>_fused_qk_rope_reshape_and_cache_kernel</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>5.679</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>27.078</v>
-      </c>
-      <c r="F12" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="G12" t="n">
-        <v>5.767</v>
-      </c>
-      <c r="H12" t="n">
-        <v>5.679</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6.999</v>
-      </c>
-      <c r="J12" t="n">
-        <v>21.116</v>
-      </c>
-      <c r="K12" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>paged_attention_decode_sliding_window</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>21.399</v>
-      </c>
-      <c r="D13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="n">
-        <v>15.349</v>
-      </c>
-      <c r="H13" t="n">
-        <v>21.039</v>
-      </c>
-      <c r="I13" t="n">
-        <v>22.719</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>triton_poi</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>triton_poi_fused_as_strided_clone_copy__0</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>6.839</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E14" t="n">
-        <v>6.839</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G14" t="n">
-        <v>5.729</v>
-      </c>
-      <c r="H14" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="I14" t="n">
-        <v>7.039</v>
-      </c>
-      <c r="J14" t="n">
-        <v>5.729</v>
-      </c>
-      <c r="K14" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>gemm_a16w16</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>aiter::bf16gemm_fp32bf16_tn_64x64_splitk_clean</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>12.76</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E15" t="n">
-        <v>12.76</v>
-      </c>
-      <c r="F15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G15" t="n">
-        <v>12.763</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12.719</v>
-      </c>
-      <c r="I15" t="n">
-        <v>13.599</v>
-      </c>
-      <c r="J15" t="n">
-        <v>12.763</v>
-      </c>
-      <c r="K15" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="n">
-        <v>273.789</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>253.711</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
         <v>520</v>
       </c>
     </row>
@@ -1032,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1065,44 +629,673 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>void ck_tile::kentry&lt;2, ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)1, ck_tile::moe::Swiglu&gt;, ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)1, ck_tile::moe::Swiglu&gt;::MoeFlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt; &gt; &gt;(ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)1, ck_tile::moe::Swiglu&gt;::MoeFlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt; &gt;)</t>
+          <t>paged_attention_decode_sliding_window</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>108.7</v>
+        <v>8.1</v>
       </c>
       <c r="D2" t="n">
-        <v>108.7</v>
+        <v>8.1</v>
       </c>
       <c r="E2" t="n">
-        <v>39.7</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>void ck_tile::kentry&lt;2, ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)2, ck_tile::moe::MoeSilu&gt;, ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)2, ck_tile::moe::MoeSilu&gt;::MoeFlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt; &gt; &gt;(ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)2, ck_tile::moe::MoeSilu&gt;::MoeFlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt; &gt;)</t>
+          <t>_fused_qk_rope_reshape_and_cache_kernel</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>61.8</v>
+        <v>5.5</v>
       </c>
       <c r="D3" t="n">
-        <v>61.8</v>
+        <v>5.5</v>
       </c>
       <c r="E3" t="n">
-        <v>22.6</v>
+        <v>40.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cpu_module</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>gpu_kernel</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>duration_us</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pct%</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sum per module</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>module_pct%</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>avg_us</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>median_us</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>p95_us</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>avg sum per module</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>n_samples</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>input_layernorm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>void aiter::add_rmsnorm_quant_kernel&lt;std::bfloat16_t, std::bfloat16_t, 256, 16, true, false, true, 1&gt;(std::bfloat16_t*, std::bfloat16_t*, float*, std::bfloat16_t*, std::bfloat16_t*, std::bfloat16_t*, double, int, int, int, int, int, int, int, bool)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5.239</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5.239</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.655</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5.479</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6.799</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5.655</v>
+      </c>
+      <c r="K2" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>q_proj_and_k_up_proj</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>aiter::bf16gemm_fp32bf16_tn_64x64_splitk_clean</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="D3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="I3" t="n">
+        <v>15.039</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="K3" t="n">
+        <v>520</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>triton_poi</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>triton_poi_fused_as_strided_clone_copy__0</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5.199</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5.199</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.664</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.479</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6.799</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.664</v>
+      </c>
+      <c r="K4" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>v_up_proj_and_o_proj</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>aiter::bf16gemm_fp32bf16_tn_64x64_splitk_clean</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>13.559</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13.559</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12.821</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12.639</v>
+      </c>
+      <c r="I5" t="n">
+        <v>13.639</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12.821</v>
+      </c>
+      <c r="K5" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>post_attn_layernorm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>_fused_add_rmsnorm_pad</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5.239</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5.239</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.565</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.399</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.679</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5.565</v>
+      </c>
+      <c r="K6" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>triton_poi</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>triton_poi_fused_as_strided_clone_1</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5.319</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5.319</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.661</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5.479</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6.799</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.661</v>
+      </c>
+      <c r="K7" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>v_up_proj_and_o_proj</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>aiter::bf16gemm_fp32bf16_tn_64x64_splitk_clean</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6.639</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6.639</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.776</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7.999</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6.776</v>
+      </c>
+      <c r="K8" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>moe_router</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>void vllm::moe::topkGatingSoftmax&lt;std::bfloat16_t, 16, 128, 8, 32, true, 0, (vllm::moe::SharedExpertScoringFunc)0&gt;(std::bfloat16_t const*, bool const*, float*, int, int*, int*, int, int, int, int, int, int)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6.879</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6.879</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.011</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.679</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6.839</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6.011</v>
+      </c>
+      <c r="K9" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mxfp4_moe</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>void ck_tile::kentry&lt;2, ck_tile::MoeSortingMultiPhaseKernel_P0_v2&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;, ck_tile::MoeSortingMultiPhaseKernel_P0_v2&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;::Kargs&gt;(ck_tile::MoeSortingMultiPhaseKernel_P0_v2&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;::Kargs)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5.159</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.518</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.651</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.479</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6.799</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11.229</v>
+      </c>
+      <c r="K10" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>void ck_tile::kentry&lt;2, ck_tile::MoeSortingMultiPhaseKernel_P23&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;, ck_tile::MoeSortingMultiPhaseKernel_P23&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;::Kargs&gt;(ck_tile::MoeSortingMultiPhaseKernel_P23&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;::Kargs)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5.359</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>5.577</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6.799</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>moe_expert_ffn</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>void ck_tile::kentry&lt;2, ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)1, ck_tile::moe::Swiglu&gt;, ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)1, ck_tile::moe::Swiglu&gt;::MoeFlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt; &gt; &gt;(ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)1, ck_tile::moe::Swiglu&gt;::MoeFlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt; &gt;)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>69.88</v>
+      </c>
+      <c r="D12" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>110.959</v>
+      </c>
+      <c r="F12" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>70.60599999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="I12" t="n">
+        <v>85.92</v>
+      </c>
+      <c r="J12" t="n">
+        <v>111.358</v>
+      </c>
+      <c r="K12" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>void ck_tile::kentry&lt;2, ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)2, ck_tile::moe::MoeSilu&gt;, ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)2, ck_tile::moe::MoeSilu&gt;::MoeFlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt; &gt; &gt;(ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)2, ck_tile::moe::MoeSilu&gt;::MoeFlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt; &gt;)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>41.079</v>
+      </c>
+      <c r="D13" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>40.753</v>
+      </c>
+      <c r="H13" t="n">
+        <v>42.479</v>
+      </c>
+      <c r="I13" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>184.47</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>184.67</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>520</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>gpu_kernel</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>calls</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>total_duration_us</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>avg_duration_us</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>void ck_tile::kentry&lt;2, ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)1, ck_tile::moe::Swiglu&gt;, ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)1, ck_tile::moe::Swiglu&gt;::MoeFlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt; &gt; &gt;(ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)1, ck_tile::moe::Swiglu&gt;::MoeFlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt; &gt;)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>void ck_tile::kentry&lt;2, ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)2, ck_tile::moe::MoeSilu&gt;, ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)2, ck_tile::moe::MoeSilu&gt;::MoeFlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt; &gt; &gt;(ck_tile::MoeFlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, 1, 1&gt;, ck_tile::F16xMXF4FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::F16xMXF4FlatmmPipelineProblem&lt;std::bfloat16_t, ck_tile::pk_float4_e2m1_t, float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;16, 128, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 32&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)2, false, std::bfloat16_t&gt;, ck_tile::F16xMXF4FlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;std::bfloat16_t, std::bfloat16_t, ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 16, 128, 1, 4, 16, 16, 32, false, 1, false, 1, 2, false&gt;, void&gt;, (ck_tile::MoeFlatmmKind)2, ck_tile::moe::MoeSilu&gt;::MoeFlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 32, ck_tile::e8m0_bexp_t&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt; &gt;)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>aiter::bf16gemm_fp32bf16_tn_64x64_splitk_clean</t>
         </is>
       </c>
@@ -1110,89 +1303,89 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.6</v>
+        <v>35.1</v>
       </c>
       <c r="D4" t="n">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="E4" t="n">
-        <v>11.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>paged_attention_decode_sliding_window</t>
+          <t>void vllm::moe::topkGatingSoftmax&lt;std::bfloat16_t, 16, 128, 8, 32, true, 0, (vllm::moe::SharedExpertScoringFunc)0&gt;(std::bfloat16_t const*, bool const*, float*, int, int*, int*, int, int, int, int, int, int)</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>21.4</v>
+        <v>6.9</v>
       </c>
       <c r="D5" t="n">
-        <v>21.4</v>
+        <v>6.9</v>
       </c>
       <c r="E5" t="n">
-        <v>7.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>triton_poi_fused_as_strided_clone_1</t>
+          <t>void ck_tile::kentry&lt;2, ck_tile::MoeSortingMultiPhaseKernel_P23&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;, ck_tile::MoeSortingMultiPhaseKernel_P23&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;::Kargs&gt;(ck_tile::MoeSortingMultiPhaseKernel_P23&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;::Kargs)</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>7.1</v>
+        <v>5.4</v>
       </c>
       <c r="D6" t="n">
-        <v>7.1</v>
+        <v>5.4</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>void aiter::add_rmsnorm_quant_kernel&lt;std::bfloat16_t, std::bfloat16_t, 256, 16, true, false, true, 1&gt;(std::bfloat16_t*, std::bfloat16_t*, float*, std::bfloat16_t*, std::bfloat16_t*, std::bfloat16_t*, double, int, int, int, int, int, int, int, bool)</t>
+          <t>triton_poi_fused_as_strided_clone_1</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="D7" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>triton_poi_fused_as_strided_clone_copy__0</t>
+          <t>void aiter::add_rmsnorm_quant_kernel&lt;std::bfloat16_t, std::bfloat16_t, 256, 16, true, false, true, 1&gt;(std::bfloat16_t*, std::bfloat16_t*, float*, std::bfloat16_t*, std::bfloat16_t*, std::bfloat16_t*, double, int, int, int, int, int, int, int, bool)</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="D8" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -1205,89 +1398,51 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="D9" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>void ck_tile::kentry&lt;2, ck_tile::MoeSortingMultiPhaseKernel_P0_v2&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;, ck_tile::MoeSortingMultiPhaseKernel_P0_v2&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;::Kargs&gt;(ck_tile::MoeSortingMultiPhaseKernel_P0_v2&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;::Kargs)</t>
+          <t>triton_poi_fused_as_strided_clone_copy__0</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="D10" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>_fused_qk_rope_reshape_and_cache_kernel</t>
+          <t>void ck_tile::kentry&lt;2, ck_tile::MoeSortingMultiPhaseKernel_P0_v2&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;, ck_tile::MoeSortingMultiPhaseKernel_P0_v2&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;::Kargs&gt;(ck_tile::MoeSortingMultiPhaseKernel_P0_v2&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;::Kargs)</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="D11" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>void vllm::moe::topkGatingSoftmax&lt;std::bfloat16_t, 16, 128, 8, 32, true, 0, (vllm::moe::SharedExpertScoringFunc)0&gt;(std::bfloat16_t const*, bool const*, float*, int, int*, int*, int, int, int, int, int, int)</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>void ck_tile::kentry&lt;2, ck_tile::MoeSortingMultiPhaseKernel_P23&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;, ck_tile::MoeSortingMultiPhaseKernel_P23&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;::Kargs&gt;(ck_tile::MoeSortingMultiPhaseKernel_P23&lt;ck_tile::MoeSortingProblemMp&lt;int, float, int, 1, false, false, true&gt; &gt;::Kargs)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
     </row>
   </sheetData>
